--- a/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
@@ -48,21 +48,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>供应商阶段</t>
-    </r>
-  </si>
-  <si>
     <t>采购员</t>
   </si>
   <si>
@@ -136,6 +121,10 @@
   </si>
   <si>
     <t>资质有效期止</t>
+  </si>
+  <si>
+    <t>支付方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -508,24 +497,23 @@
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
     <col min="2" max="2" width="34.75" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="5" width="32.625" customWidth="1"/>
-    <col min="6" max="6" width="27.875" customWidth="1"/>
-    <col min="7" max="7" width="21.75" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="12" width="11.25" customWidth="1"/>
-    <col min="13" max="13" width="18.625" customWidth="1"/>
-    <col min="14" max="14" width="17.625" customWidth="1"/>
-    <col min="15" max="15" width="21" customWidth="1"/>
-    <col min="16" max="16" width="18.625" customWidth="1"/>
-    <col min="17" max="17" width="15.875" customWidth="1"/>
-    <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="26.75" customWidth="1"/>
-    <col min="21" max="21" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="32.625" customWidth="1"/>
+    <col min="5" max="5" width="27.875" customWidth="1"/>
+    <col min="6" max="6" width="21.75" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="11" width="11.25" customWidth="1"/>
+    <col min="12" max="12" width="18.625" customWidth="1"/>
+    <col min="13" max="13" width="17.625" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="18.625" customWidth="1"/>
+    <col min="16" max="16" width="15.875" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="26.75" customWidth="1"/>
+    <col min="20" max="21" width="19.75" customWidth="1"/>
     <col min="22" max="22" width="16.25" customWidth="1"/>
     <col min="23" max="23" width="17" customWidth="1"/>
     <col min="24" max="24" width="21" customWidth="1"/>
@@ -533,14 +521,14 @@
     <col min="26" max="26" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -549,16 +537,16 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -595,22 +583,22 @@
         <v>19</v>
       </c>
       <c r="U1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="Z1" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.15">
@@ -627,8 +615,8 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>

--- a/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
@@ -1,24 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22560" windowHeight="11250"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -34,6 +52,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -81,6 +106,81 @@
     <t>供应商分类</t>
   </si>
   <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>工厂所在地</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>公司注册资金（万）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商品类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>体系认证</t>
+    </r>
+  </si>
+  <si>
     <t>联系人</t>
   </si>
   <si>
@@ -114,6 +214,9 @@
     <t>银行账号</t>
   </si>
   <si>
+    <t>支付方式</t>
+  </si>
+  <si>
     <t>资质名称</t>
   </si>
   <si>
@@ -121,17 +224,19 @@
   </si>
   <si>
     <t>资质有效期止</t>
-  </si>
-  <si>
-    <t>支付方式</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,21 +252,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -169,9 +598,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -179,9 +850,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -191,11 +859,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -486,14 +1204,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
     <col min="2" max="2" width="34.75" customWidth="1"/>
@@ -504,156 +1222,159 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="17.125" customWidth="1"/>
-    <col min="10" max="11" width="11.25" customWidth="1"/>
-    <col min="12" max="12" width="18.625" customWidth="1"/>
-    <col min="13" max="13" width="17.625" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="18.625" customWidth="1"/>
-    <col min="16" max="16" width="15.875" customWidth="1"/>
-    <col min="17" max="17" width="14.75" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="26.75" customWidth="1"/>
-    <col min="20" max="21" width="19.75" customWidth="1"/>
-    <col min="22" max="22" width="16.25" customWidth="1"/>
-    <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="21" customWidth="1"/>
-    <col min="25" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="11.125" customWidth="1"/>
+    <col min="10" max="10" width="21.625" customWidth="1"/>
+    <col min="11" max="11" width="22.5" customWidth="1"/>
+    <col min="12" max="12" width="20.875" customWidth="1"/>
+    <col min="13" max="13" width="18.375" customWidth="1"/>
+    <col min="14" max="14" width="17.375" customWidth="1"/>
+    <col min="15" max="16" width="11.25" customWidth="1"/>
+    <col min="17" max="17" width="18.625" customWidth="1"/>
+    <col min="18" max="18" width="17.625" customWidth="1"/>
+    <col min="19" max="19" width="21" customWidth="1"/>
+    <col min="20" max="20" width="18.625" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="14.75" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="26.75" customWidth="1"/>
+    <col min="25" max="26" width="19.75" customWidth="1"/>
+    <col min="27" max="27" width="16.25" customWidth="1"/>
+    <col min="28" max="28" width="17" customWidth="1"/>
+    <col min="29" max="29" width="21" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="35.25" customHeight="1" spans="1:31">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="W1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>15</v>
+      <c r="AB1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
+    <row r="2" spans="1:31">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <r>
       <rPr>
@@ -97,15 +97,6 @@
     </r>
   </si>
   <si>
-    <t>结算方式</t>
-  </si>
-  <si>
-    <t>结算币种</t>
-  </si>
-  <si>
-    <t>供应商分类</t>
-  </si>
-  <si>
     <r>
       <t>*</t>
     </r>
@@ -117,11 +108,70 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>结算方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结算币种</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商分类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>工厂所在地</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -137,6 +187,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -162,11 +219,33 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>供应商品类</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>产品分类-二级分类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>应用分类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -846,7 +925,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -854,9 +933,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1210,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -1226,25 +1302,25 @@
     <col min="11" max="11" width="22.5" customWidth="1"/>
     <col min="12" max="12" width="20.875" customWidth="1"/>
     <col min="13" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="14" width="17.375" customWidth="1"/>
-    <col min="15" max="16" width="11.25" customWidth="1"/>
-    <col min="17" max="17" width="18.625" customWidth="1"/>
-    <col min="18" max="18" width="17.625" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="20" width="18.625" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="14.75" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="26.75" customWidth="1"/>
-    <col min="25" max="26" width="19.75" customWidth="1"/>
-    <col min="27" max="27" width="16.25" customWidth="1"/>
-    <col min="28" max="28" width="17" customWidth="1"/>
-    <col min="29" max="29" width="21" customWidth="1"/>
-    <col min="30" max="30" width="18" customWidth="1"/>
-    <col min="31" max="31" width="11.125" customWidth="1"/>
+    <col min="14" max="15" width="17.375" customWidth="1"/>
+    <col min="16" max="17" width="11.25" customWidth="1"/>
+    <col min="18" max="18" width="18.625" customWidth="1"/>
+    <col min="19" max="19" width="17.625" customWidth="1"/>
+    <col min="20" max="20" width="21" customWidth="1"/>
+    <col min="21" max="21" width="18.625" customWidth="1"/>
+    <col min="22" max="22" width="15.875" customWidth="1"/>
+    <col min="23" max="23" width="14.75" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="26.75" customWidth="1"/>
+    <col min="26" max="27" width="19.75" customWidth="1"/>
+    <col min="28" max="28" width="16.25" customWidth="1"/>
+    <col min="29" max="29" width="17" customWidth="1"/>
+    <col min="30" max="30" width="21" customWidth="1"/>
+    <col min="31" max="31" width="18" customWidth="1"/>
+    <col min="32" max="32" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:31">
+    <row r="1" ht="35.25" customHeight="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,13 +1339,13 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1287,7 +1363,7 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
@@ -1324,10 +1400,10 @@
         <v>25</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>27</v>
@@ -1336,41 +1412,45 @@
         <v>28</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
+    <row r="2" spans="1:32">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <r>
       <rPr>
@@ -83,6 +83,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -98,6 +105,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -113,6 +127,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -128,6 +149,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -209,6 +237,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -224,6 +259,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -236,6 +278,23 @@
       </rPr>
       <t>应用分类</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>付款条件</t>
+    </r>
+  </si>
+  <si>
+    <t>税率</t>
   </si>
   <si>
     <r>
@@ -315,7 +374,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +385,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -795,137 +860,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -937,6 +1002,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1286,7 +1354,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -1302,25 +1370,25 @@
     <col min="11" max="11" width="22.5" customWidth="1"/>
     <col min="12" max="12" width="20.875" customWidth="1"/>
     <col min="13" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="15" width="17.375" customWidth="1"/>
-    <col min="16" max="17" width="11.25" customWidth="1"/>
-    <col min="18" max="18" width="18.625" customWidth="1"/>
-    <col min="19" max="19" width="17.625" customWidth="1"/>
-    <col min="20" max="20" width="21" customWidth="1"/>
-    <col min="21" max="21" width="18.625" customWidth="1"/>
-    <col min="22" max="22" width="15.875" customWidth="1"/>
-    <col min="23" max="23" width="14.75" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="26.75" customWidth="1"/>
-    <col min="26" max="27" width="19.75" customWidth="1"/>
-    <col min="28" max="28" width="16.25" customWidth="1"/>
-    <col min="29" max="29" width="17" customWidth="1"/>
-    <col min="30" max="30" width="21" customWidth="1"/>
-    <col min="31" max="31" width="18" customWidth="1"/>
-    <col min="32" max="32" width="11.125" customWidth="1"/>
+    <col min="14" max="17" width="17.375" customWidth="1"/>
+    <col min="18" max="19" width="11.25" customWidth="1"/>
+    <col min="20" max="20" width="18.625" customWidth="1"/>
+    <col min="21" max="21" width="17.625" customWidth="1"/>
+    <col min="22" max="22" width="21" customWidth="1"/>
+    <col min="23" max="23" width="18.625" customWidth="1"/>
+    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="25" max="25" width="14.75" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="26.75" customWidth="1"/>
+    <col min="28" max="29" width="19.75" customWidth="1"/>
+    <col min="30" max="30" width="16.25" customWidth="1"/>
+    <col min="31" max="31" width="17" customWidth="1"/>
+    <col min="32" max="32" width="21" customWidth="1"/>
+    <col min="33" max="33" width="18" customWidth="1"/>
+    <col min="34" max="34" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:32">
+    <row r="1" ht="35.25" customHeight="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,10 +1434,10 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
@@ -1403,22 +1471,28 @@
         <v>26</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE1" s="2" t="s">
         <v>29</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:34">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1438,9 +1512,9 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
-      <c r="T2" s="2"/>
+      <c r="T2" s="3"/>
       <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
+      <c r="V2" s="2"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
@@ -1451,6 +1525,8 @@
       <c r="AD2" s="3"/>
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <r>
       <rPr>
@@ -73,7 +73,10 @@
     </r>
   </si>
   <si>
-    <t>采购员</t>
+    <t>采购开发员</t>
+  </si>
+  <si>
+    <t>采购跟单员</t>
   </si>
   <si>
     <t>公司地址</t>
@@ -281,6 +284,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1354,41 +1364,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
     <col min="2" max="2" width="34.75" customWidth="1"/>
-    <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="32.625" customWidth="1"/>
-    <col min="5" max="5" width="27.875" customWidth="1"/>
-    <col min="6" max="6" width="21.75" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="17.125" customWidth="1"/>
-    <col min="10" max="10" width="21.625" customWidth="1"/>
-    <col min="11" max="11" width="22.5" customWidth="1"/>
-    <col min="12" max="12" width="20.875" customWidth="1"/>
-    <col min="13" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="17" width="17.375" customWidth="1"/>
-    <col min="18" max="19" width="11.25" customWidth="1"/>
-    <col min="20" max="20" width="18.625" customWidth="1"/>
-    <col min="21" max="21" width="17.625" customWidth="1"/>
-    <col min="22" max="22" width="21" customWidth="1"/>
-    <col min="23" max="23" width="18.625" customWidth="1"/>
-    <col min="24" max="24" width="15.875" customWidth="1"/>
-    <col min="25" max="25" width="14.75" customWidth="1"/>
-    <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="27" max="27" width="26.75" customWidth="1"/>
-    <col min="28" max="29" width="19.75" customWidth="1"/>
-    <col min="30" max="30" width="16.25" customWidth="1"/>
-    <col min="31" max="31" width="17" customWidth="1"/>
-    <col min="32" max="32" width="21" customWidth="1"/>
-    <col min="33" max="33" width="18" customWidth="1"/>
-    <col min="34" max="34" width="11.125" customWidth="1"/>
+    <col min="3" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="32.625" customWidth="1"/>
+    <col min="6" max="6" width="27.875" customWidth="1"/>
+    <col min="7" max="7" width="21.75" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="17.125" customWidth="1"/>
+    <col min="11" max="11" width="21.625" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="18.375" customWidth="1"/>
+    <col min="15" max="18" width="17.375" customWidth="1"/>
+    <col min="19" max="20" width="11.25" customWidth="1"/>
+    <col min="21" max="21" width="18.625" customWidth="1"/>
+    <col min="22" max="22" width="17.625" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="24" width="18.625" customWidth="1"/>
+    <col min="25" max="25" width="15.875" customWidth="1"/>
+    <col min="26" max="26" width="14.75" customWidth="1"/>
+    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="28" max="28" width="26.75" customWidth="1"/>
+    <col min="29" max="30" width="19.75" customWidth="1"/>
+    <col min="31" max="31" width="16.25" customWidth="1"/>
+    <col min="32" max="32" width="17" customWidth="1"/>
+    <col min="33" max="33" width="21" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
+    <col min="35" max="35" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:34">
+    <row r="1" ht="35.25" customHeight="1" spans="1:35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1414,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1434,13 +1444,13 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
@@ -1477,10 +1487,10 @@
         <v>28</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>30</v>
@@ -1489,10 +1499,13 @@
         <v>31</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:35">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1514,8 +1527,8 @@
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="2"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -1527,6 +1540,7 @@
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
@@ -27,7 +27,94 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商等级</t>
+    </r>
+  </si>
+  <si>
+    <t>采购开发员</t>
+  </si>
+  <si>
+    <t>采购跟单员</t>
+  </si>
+  <si>
+    <t>公司地址</t>
+  </si>
+  <si>
+    <t>公司网址</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结算方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结算币种</t>
+    </r>
+  </si>
   <si>
     <r>
       <rPr>
@@ -47,7 +134,22 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>供应商名称</t>
+      <t>供应商分类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>工厂所在地</t>
     </r>
   </si>
   <si>
@@ -69,20 +171,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>供应商等级</t>
-    </r>
-  </si>
-  <si>
-    <t>采购开发员</t>
-  </si>
-  <si>
-    <t>采购跟单员</t>
-  </si>
-  <si>
-    <t>公司地址</t>
-  </si>
-  <si>
-    <t>公司网址</t>
+      <t>公司注册资金（万）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -103,7 +193,22 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>供应商状态</t>
+      <t>供应商属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品分类-二级分类</t>
     </r>
   </si>
   <si>
@@ -125,8 +230,25 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>结算方式</t>
-    </r>
+      <t>应用分类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>付款条件</t>
+    </r>
+  </si>
+  <si>
+    <t>税率（%）</t>
   </si>
   <si>
     <r>
@@ -147,184 +269,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>结算币种</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>供应商分类</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>工厂所在地</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公司注册资金（万）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>供应商属性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>产品分类-二级分类</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>应用分类</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>付款条件</t>
-    </r>
-  </si>
-  <si>
-    <t>税率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>体系认证</t>
     </r>
   </si>
@@ -347,7 +291,7 @@
     <t>状态</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>联系人备注</t>
   </si>
   <si>
     <t>账户名称</t>
@@ -365,6 +309,9 @@
     <t>支付方式</t>
   </si>
   <si>
+    <t>账户备注</t>
+  </si>
+  <si>
     <t>资质名称</t>
   </si>
   <si>
@@ -372,6 +319,9 @@
   </si>
   <si>
     <t>资质有效期止</t>
+  </si>
+  <si>
+    <t>资质备注</t>
   </si>
 </sst>
 </file>
@@ -1490,19 +1440,19 @@
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:35">

--- a/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplier.xlsx
@@ -281,6 +281,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -294,7 +301,7 @@
     </r>
   </si>
   <si>
-    <t>税率</t>
+    <t>税率（%）</t>
   </si>
   <si>
     <r>
